--- a/reports/telegram/aegis_daily_2026-08-19.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV27"/>
+  <dimension ref="A1:AV20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R2-GNFC-IND-20260806-abf3d2</t>
+          <t>R2-BMY-USA-20260819-1d7adb</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GNFC_IND_20260806</t>
+          <t>BMY_USA_20260819</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>80.3</v>
+        <v>79.8</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,24 +783,24 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>33.3</v>
+        <v>61.4</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD→STRONG · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 62% · band HOLD · 60d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>34.1</v>
+        <v>62.2</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,73 +808,73 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>34.5</v>
+        <v>38</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>609.75</v>
+        <v>68.22</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>553.3</v>
+        <v>68.22</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>603.65</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>615.85</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>573.16</v>
+        <v>64.13</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>3.59</v>
+        <v>-6</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>682.92</v>
+        <v>76.41</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>23.43</v>
+        <v>12.01</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>756.09</v>
+        <v>84.59</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>36.65</v>
+        <v>24</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>600.65</v>
+        <v>66.05</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>1.52</v>
+        <v>3.29</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Value · Trend · Ai Hybrid</t>
+          <t>Trend · Growth · Event Driven</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr"/>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260801-4d1b4f</t>
+          <t>R2-IT-USA-20260819-1094c2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260801</t>
+          <t>IT_USA_20260819</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -908,24 +908,20 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
@@ -934,27 +930,37 @@
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 82% · momentum → · 61d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 52% · band STRONG · 60d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -962,61 +968,63 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="X3" s="3" t="inlineStr"/>
+        <v>30.6</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>1412</v>
+        <v>191.24</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>1438.5</v>
+        <v>191.24</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1373</v>
+        <v>189.32</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>1451</v>
+        <v>193.15</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>1341.4</v>
+        <v>179.76</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>-6.75</v>
+        <v>-6</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>1487</v>
+        <v>214.18</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>3.37</v>
+        <v>12</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>1591.09</v>
+        <v>237.13</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>10.61</v>
+        <v>24</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>1415.3</v>
+        <v>182.07</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>-0.23</v>
+        <v>5.03</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="3" t="n">
         <v>0</v>
@@ -1024,33 +1032,33 @@
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Growth</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-SUNPHARMA-IND-20260801-6c9af2</t>
+          <t>R2-PLTR-USA-20260819-03944e</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA_IND_20260801</t>
+          <t>PLTR_USA_20260819</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1060,119 +1068,123 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Sun Pharma</t>
-        </is>
-      </c>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 56% · band HOLD · 11d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-6.9% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>169.27</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>172.69</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>160.72</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="n">
-        <v>1875.1</v>
-      </c>
-      <c r="AD4" s="3" t="n">
-        <v>2014.8</v>
-      </c>
-      <c r="AE4" s="3" t="n">
-        <v>1824</v>
-      </c>
-      <c r="AF4" s="3" t="n">
-        <v>1926</v>
-      </c>
-      <c r="AG4" s="3" t="n">
-        <v>1781.345</v>
-      </c>
-      <c r="AH4" s="3" t="n">
-        <v>-11.59</v>
-      </c>
-      <c r="AI4" s="3" t="n">
-        <v>1961</v>
-      </c>
-      <c r="AJ4" s="3" t="n">
-        <v>-2.67</v>
-      </c>
       <c r="AK4" s="3" t="n">
-        <v>2098.27</v>
+        <v>212.02</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>4.14</v>
+        <v>24</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1882</v>
+        <v>171.54</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.33</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-6.93</v>
+        <v>0</v>
       </c>
       <c r="AP4" s="3" t="n">
         <v>0</v>
@@ -1180,33 +1192,33 @@
       <c r="AQ4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Value · Quality · Growth</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr"/>
       <c r="AT4" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>-2.67</v>
+        <v>0</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-PIDILITIND-IND-20260801-40d265</t>
+          <t>R2-GOOGL-USA-20260819-f7860e</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND_IND_20260801</t>
+          <t>GOOGL_USA_20260819</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1216,53 +1228,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Pidilite</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>→ BMY · +9.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 51 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
+          <t>🔴 AVOID · Rank #8 · Conf 56% · band HOLD · 60d left · → EXIT (rotate to BMY)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>86</v>
+        <v>55.6</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1270,61 +1298,63 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="X5" s="3" t="inlineStr"/>
+        <v>28.2</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>1674</v>
+        <v>342.85</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1625.5</v>
+        <v>342.85</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>1621</v>
+        <v>339.42</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1727</v>
+        <v>346.28</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>1590.3</v>
+        <v>325.71</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>-2.17</v>
+        <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>1697</v>
+        <v>370.28</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>1815.79</v>
+        <v>394.28</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>11.71</v>
+        <v>15</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>1669</v>
+        <v>344.2</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.3</v>
+        <v>-0.39</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="3" t="n">
         <v>0</v>
@@ -1332,33 +1362,31 @@
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Growth · Event Driven</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>4.4</v>
+        <v>9.77</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-NTPC-IND-20260731-68aa1e</t>
+          <t>R2-ADBE-USA-20260819-ee148d</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NTPC_IND_20260731</t>
+          <t>ADBE_USA_20260819</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1368,53 +1396,69 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>→ BMY · +9.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.6%) · Rank → 4→4 · Conf 72% · momentum → · 61d left · → BUY</t>
+          <t>🔴 AVOID · Rank #9 · Conf 62% · band STRONG · 60d left · → EXIT (rotate to BMY)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>72</v>
+        <v>62.2</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1422,61 +1466,63 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="X6" s="3" t="inlineStr"/>
+        <v>28.1</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>337.1</v>
+        <v>270.51</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>345.75</v>
+        <v>270.51</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>329</v>
+        <v>267.8</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>346</v>
+        <v>273.22</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>320.245</v>
+        <v>256.98</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-7.38</v>
+        <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>364.068</v>
+        <v>292.15</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>389.5527600000001</v>
+        <v>311.09</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>12.67</v>
+        <v>15</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>337</v>
+        <v>263.14</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.03</v>
+        <v>2.8</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AP6" s="3" t="n">
         <v>0</v>
@@ -1484,33 +1530,31 @@
       <c r="AQ6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>News · Momentum · Quality</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
       <c r="AU6" s="3" t="n">
-        <v>5.3</v>
+        <v>9.91</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-LUPIN-IND-20260731-dc0229</t>
+          <t>R2-FOX-USA-20260819-04fdf5</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260731</t>
+          <t>FOX_USA_20260819</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1520,57 +1564,65 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Lupin</t>
-        </is>
-      </c>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>→ BMY · +9.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 3→5 · Conf 67% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-7.7% ≤ -5.0% · exit</t>
-        </is>
-      </c>
+          <t>🔴 AVOID · Rank #10 · Conf 56% · band HOLD · 60d left · → EXIT (rotate to BMY)</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1578,95 +1630,95 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="X7" s="3" t="inlineStr"/>
+        <v>28.1</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y7" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>2232</v>
+        <v>61.32</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>2417</v>
+        <v>61.32</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>2173</v>
+        <v>60.71</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>2291</v>
+        <v>61.93</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>2120.4</v>
+        <v>58.25</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-12.27</v>
+        <v>-5.01</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>2410.56</v>
+        <v>66.23</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>-0.27</v>
+        <v>8.01</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>2579.2992</v>
+        <v>70.52</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>6.71</v>
+        <v>15</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>2259</v>
+        <v>61.23</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-1.2</v>
+        <v>0.15</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-7.65</v>
+        <v>0</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Trend · Event Driven · Value</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="n">
-        <v>-0.27</v>
+        <v>9.92</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260801-25686f</t>
+          <t>R2-FE-USA-20260819-bc8cd9</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260801</t>
+          <t>FE_USA_20260819</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1676,53 +1728,65 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>→ BMY · +63.2pp alpha</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank ↑ 8→6 · Conf 66% · momentum → · 61d left · → BUY</t>
+          <t>🔴 AVOID · Rank #11 · Conf 34% · band EXIT · 60d left · → EXIT (rotate to BMY)</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>66</v>
+        <v>34.2</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1730,61 +1794,63 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="X8" s="3" t="inlineStr"/>
+        <v>-25.2</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>412</v>
+        <v>47.3</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>388.7</v>
+        <v>47.3</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>399</v>
+        <v>46.83</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>425</v>
+        <v>47.77</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>391.4</v>
+        <v>44.93</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>-5.01</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>444.96</v>
+        <v>51.08</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>14.47</v>
+        <v>7.99</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>476.1072000000001</v>
+        <v>54.39</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>22.49</v>
+        <v>14.99</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>412.45</v>
+        <v>47.26</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="3" t="n">
         <v>0</v>
@@ -1792,33 +1858,31 @@
       <c r="AQ8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
       <c r="AU8" s="3" t="n">
-        <v>14.47</v>
+        <v>63.22</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-POWERGRID-IND-20260801-1188ad</t>
+          <t>R1-PLTR-USA-20260819-b11807</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID_IND_20260801</t>
+          <t>PLTR_USA_20260819</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1828,7 +1892,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1838,14 +1902,10 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Power Grid</t>
-        </is>
-      </c>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1854,31 +1914,37 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.2%) · Rank → 7→7 · Conf 69% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-6.3% ≤ -5.0% · exit</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 56% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1886,61 +1952,61 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>57</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>169.27</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>172.69</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>162.431</v>
+      </c>
+      <c r="AH9" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI9" s="3" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="AJ9" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA9" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="AC9" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="AD9" s="3" t="n">
-        <v>285.9</v>
-      </c>
-      <c r="AE9" s="3" t="n">
-        <v>262</v>
-      </c>
-      <c r="AF9" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="AG9" s="3" t="n">
-        <v>254.6</v>
-      </c>
-      <c r="AH9" s="3" t="n">
-        <v>-10.95</v>
-      </c>
-      <c r="AI9" s="3" t="n">
-        <v>289.44</v>
-      </c>
-      <c r="AJ9" s="3" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK9" s="3" t="n">
-        <v>309.7008</v>
+        <v>204.905</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>8.32</v>
+        <v>19.84</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>266.15</v>
+        <v>171.54</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.7</v>
+        <v>-0.33</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-6.26</v>
+        <v>0</v>
       </c>
       <c r="AP9" s="3" t="n">
         <v>0</v>
@@ -1951,30 +2017,30 @@
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>1.24</v>
+        <v>12</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260819-6db98c</t>
+          <t>R1-BMY-USA-20260819-a9408a</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260819</t>
+          <t>BMY_USA_20260819</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1984,7 +2050,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1994,7 +2060,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -2006,23 +2072,37 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #8 · Conf 67% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 62% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>67</v>
+        <v>62.2</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2030,17 +2110,17 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>53</v>
+        <v>68.2</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
@@ -2048,73 +2128,77 @@
         </is>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>239.5</v>
+        <v>68.22</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>239.5</v>
+        <v>68.22</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>232</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>247</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>227.525</v>
+        <v>64.809</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>258.66</v>
+        <v>76.41</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>8</v>
+        <v>12.01</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>276.7662</v>
+        <v>81.7587</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>15.56</v>
+        <v>19.85</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>238.49</v>
+        <v>66.05</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.42</v>
+        <v>3.29</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR10" s="3" t="inlineStr"/>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>8</v>
+        <v>12.01</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260731-0f9978</t>
+          <t>R1-IT-USA-20260819-1791f6</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260731</t>
+          <t>IT_USA_20260819</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2124,7 +2208,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2134,14 +2218,10 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Coal India</t>
-        </is>
-      </c>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -2150,27 +2230,37 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank ↑ 10→9 · Conf 66% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 52% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2178,95 +2268,95 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>52</v>
+        <v>58.5</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>406.9</v>
+        <v>191.24</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>411.3</v>
+        <v>191.24</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>395</v>
+        <v>189.32</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>419</v>
+        <v>193.15</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>386.5549999999999</v>
+        <v>181.678</v>
       </c>
       <c r="AH11" s="3" t="n">
-        <v>-6.02</v>
+        <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>439.452</v>
+        <v>214.18</v>
       </c>
       <c r="AJ11" s="3" t="n">
-        <v>6.84</v>
+        <v>12</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>470.21364</v>
+        <v>229.1726</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>14.32</v>
+        <v>19.84</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>408.45</v>
+        <v>182.07</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>-0.38</v>
+        <v>5.03</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>-1.07</v>
+        <v>0</v>
       </c>
       <c r="AP11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR11" s="3" t="inlineStr"/>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT11" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>6.84</v>
+        <v>12</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260731-27437b</t>
+          <t>R1-ADBE-USA-20260819-821383</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260731</t>
+          <t>ADBE_USA_20260819</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2276,7 +2366,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2286,43 +2376,53 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 62% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>66</v>
+        <v>62.2</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2330,61 +2430,61 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>493</v>
+        <v>270.51</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>494.35</v>
+        <v>270.51</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>478</v>
+        <v>265.1</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>508</v>
+        <v>275.92</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>468.35</v>
+        <v>256.9845</v>
       </c>
       <c r="AH12" s="3" t="n">
-        <v>-5.26</v>
+        <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>532.4400000000001</v>
+        <v>292.1508</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>7.71</v>
+        <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>569.7108000000001</v>
+        <v>312.601356</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>15.24</v>
+        <v>15.56</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>499.95</v>
+        <v>263.14</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-1.38</v>
+        <v>2.8</v>
       </c>
       <c r="AO12" s="3" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="AP12" s="3" t="n">
         <v>0</v>
@@ -2395,30 +2495,30 @@
       <c r="AR12" s="3" t="inlineStr"/>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT12" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>7.71</v>
+        <v>8</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R1-ITC-IND-20260731-71ef92</t>
+          <t>R1-EIX-USA-20260819-a1dc13</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260731</t>
+          <t>EIX_USA_20260819</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2428,7 +2528,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2438,14 +2538,10 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -2454,23 +2550,37 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.2%) · Rank #11 · Conf 70% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 62% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>70</v>
+        <v>62.2</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2478,64 +2588,64 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>50</v>
+        <v>53.9</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>270</v>
+        <v>74.31</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>282.9</v>
+        <v>74.31</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>264</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>276</v>
+        <v>75.8</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>256.5</v>
+        <v>70.5945</v>
       </c>
       <c r="AH13" s="3" t="n">
-        <v>-9.33</v>
+        <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>271</v>
+        <v>80.2548</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>-4.21</v>
+        <v>8</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>289.97</v>
+        <v>85.87263600000001</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>2.5</v>
+        <v>15.56</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>273.05</v>
+        <v>73.69</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-1.12</v>
+        <v>0.85</v>
       </c>
       <c r="AO13" s="3" t="n">
-        <v>-4.56</v>
+        <v>0</v>
       </c>
       <c r="AP13" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="3" t="n">
         <v>0</v>
@@ -2543,30 +2653,30 @@
       <c r="AR13" s="3" t="inlineStr"/>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT13" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>-4.21</v>
+        <v>8</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R1-HINDUNILVR-IND-20260819-53db86</t>
+          <t>R1-MSFT-USA-20260819-f1d458</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR_IND_20260819</t>
+          <t>MSFT_USA_20260819</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2576,7 +2686,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2586,10 +2696,14 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2598,23 +2712,37 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #12 · Conf 65% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 59% · momentum → · band HOLD→STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>65</v>
+        <v>58.9</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2622,17 +2750,17 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>48</v>
+        <v>48.7</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
@@ -2640,50 +2768,54 @@
         </is>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>2035</v>
+        <v>483.32</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>2035</v>
+        <v>483.32</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>1973</v>
+        <v>473.65</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>2097</v>
+        <v>492.99</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>1933.25</v>
+        <v>459.154</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>2197.8</v>
+        <v>521.9856</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>2351.646</v>
+        <v>558.524592</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>2055</v>
+        <v>481.63</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-0.97</v>
+        <v>0.35</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR14" s="3" t="inlineStr"/>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT14" s="3" t="n">
@@ -2694,19 +2826,19 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-LUPIN-IND-20260731-7c5f4d</t>
+          <t>R1-UBER-USA-20260819-a702c0</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260731</t>
+          <t>UBER_USA_20260819</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2716,24 +2848,20 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Lupin</t>
-        </is>
-      </c>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2742,27 +2870,37 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>51.8</v>
+        <v>59.1</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2770,89 +2908,95 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>2417</v>
+        <v>76.62</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>2417</v>
+        <v>76.62</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>2392.83</v>
+        <v>75.09</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>2441.17</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>2296.15</v>
+        <v>72.789</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>2610.36</v>
+        <v>82.74960000000002</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>2779.55</v>
+        <v>88.54207200000002</v>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>2259</v>
+        <v>74.66</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-1.2</v>
+        <v>2.63</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP15" s="3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260731-1612fe</t>
+          <t>R1-GOOGL-USA-20260819-063f97</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260731</t>
+          <t>GOOGL_USA_20260819</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2862,22 +3006,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Chambal Fert.</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2890,25 +3034,35 @@
       <c r="K16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 51 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 56% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>38.3</v>
+        <v>55.6</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2916,89 +3070,95 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>22.4</v>
+        <v>45.9</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>443.35</v>
+        <v>342.85</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>443.35</v>
+        <v>342.85</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>438.92</v>
+        <v>335.99</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>447.78</v>
+        <v>349.71</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>421.1825</v>
+        <v>325.7075</v>
       </c>
       <c r="AH16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>478.818</v>
+        <v>370.2780000000001</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>509.8525</v>
+        <v>396.1974600000001</v>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM16" s="3" t="n">
-        <v>439.05</v>
+        <v>344.2</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.39</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R1-FOX-USA-20260819-51875e</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>FOX_USA_20260819</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3008,24 +3168,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Punjab Natl. Bank</t>
-        </is>
-      </c>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3034,27 +3190,37 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 56% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>32.1</v>
+        <v>56</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -3062,58 +3228,58 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>22.2</v>
+        <v>36.3</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>113.36</v>
+        <v>61.32</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>113.36</v>
+        <v>61.32</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>112.23</v>
+        <v>60.09</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>114.49</v>
+        <v>62.55</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>107.692</v>
+        <v>58.254</v>
       </c>
       <c r="AH17" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>122.4288</v>
+        <v>66.2256</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>130.364</v>
+        <v>70.86139200000001</v>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>117.32</v>
+        <v>61.23</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-0.7</v>
+        <v>0.15</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>0</v>
@@ -3122,29 +3288,35 @@
         <v>0</v>
       </c>
       <c r="AQ17" s="3" t="n">
-        <v>-2.01</v>
+        <v>0</v>
       </c>
       <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R2-COALINDIA-IND-20260731-0fbb46</t>
+          <t>R1-SAIC-USA-20260819-ecf4b6</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260731</t>
+          <t>SAIC_USA_20260819</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3154,24 +3326,20 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Coal India</t>
-        </is>
-      </c>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3180,27 +3348,37 @@
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="n">
-        <v>36.1</v>
+        <v>59.1</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3208,58 +3386,58 @@
         </is>
       </c>
       <c r="W18" s="3" t="n">
-        <v>22.2</v>
+        <v>33.7</v>
       </c>
       <c r="X18" s="3" t="inlineStr"/>
       <c r="Y18" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>411.3</v>
+        <v>127.63</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>411.3</v>
+        <v>127.63</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>407.19</v>
+        <v>125.08</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>415.41</v>
+        <v>130.18</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>390.735</v>
+        <v>121.2485</v>
       </c>
       <c r="AH18" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>444.2040000000001</v>
+        <v>137.8404</v>
       </c>
       <c r="AJ18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>472.995</v>
+        <v>147.489228</v>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM18" s="3" t="n">
-        <v>408.45</v>
+        <v>125.95</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>-0.38</v>
+        <v>1.33</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>0</v>
@@ -3268,29 +3446,35 @@
         <v>0</v>
       </c>
       <c r="AQ18" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260731-0f7384</t>
+          <t>R2-TRV-USA-20260819-086fd4</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260731</t>
+          <t>TRV_USA_20260819</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3300,7 +3484,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -3310,12 +3494,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3326,13 +3510,13 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr"/>
@@ -3341,12 +3525,12 @@
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
-        <v>38.3</v>
+        <v>56.8</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -3354,11 +3538,11 @@
         </is>
       </c>
       <c r="W19" s="3" t="n">
-        <v>21.6</v>
+        <v>29.2</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>60</v>
@@ -3366,77 +3550,45 @@
       <c r="AA19" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB19" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AC19" s="3" t="n">
-        <v>282.9</v>
-      </c>
-      <c r="AD19" s="3" t="n">
-        <v>282.9</v>
-      </c>
-      <c r="AE19" s="3" t="n">
-        <v>280.07</v>
-      </c>
-      <c r="AF19" s="3" t="n">
-        <v>285.73</v>
-      </c>
-      <c r="AG19" s="3" t="n">
-        <v>268.7549999999999</v>
-      </c>
-      <c r="AH19" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI19" s="3" t="n">
-        <v>305.532</v>
-      </c>
-      <c r="AJ19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>325.3349999999999</v>
-      </c>
-      <c r="AL19" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
       <c r="AM19" s="3" t="n">
-        <v>273.05</v>
+        <v>367.93</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="AO19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" s="3" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AQ19" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr"/>
       <c r="AS19" s="3" t="inlineStr"/>
       <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU19" s="3" t="inlineStr"/>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R2-V-USA-20260819-b120db</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>V_USA_20260819</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3446,7 +3598,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3456,12 +3608,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Bata India</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -3472,10 +3624,10 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
@@ -3487,12 +3639,12 @@
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>24</v>
+        <v>53.6</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -3500,11 +3652,11 @@
         </is>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-30.3</v>
+        <v>27.8</v>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>60</v>
@@ -3512,1064 +3664,38 @@
       <c r="AA20" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC20" s="3" t="n">
-        <v>709</v>
-      </c>
-      <c r="AD20" s="3" t="n">
-        <v>709</v>
-      </c>
-      <c r="AE20" s="3" t="n">
-        <v>701.91</v>
-      </c>
-      <c r="AF20" s="3" t="n">
-        <v>716.09</v>
-      </c>
-      <c r="AG20" s="3" t="n">
-        <v>673.55</v>
-      </c>
-      <c r="AH20" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI20" s="3" t="n">
-        <v>765.72</v>
-      </c>
-      <c r="AJ20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>815.3499999999999</v>
-      </c>
-      <c r="AL20" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="n">
-        <v>758.1</v>
+        <v>364.25</v>
       </c>
       <c r="AN20" s="3" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="AO20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="3" t="n">
-        <v>-1.5</v>
-      </c>
+        <v>1.47</v>
+      </c>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
       <c r="AS20" s="3" t="inlineStr"/>
       <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU20" s="3" t="inlineStr"/>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>R2-PERSISTENT-IND-20260731-88d624</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>PERSISTENT_IND_20260731</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="3" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA21" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB21" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AC21" s="3" t="n">
-        <v>5322.4</v>
-      </c>
-      <c r="AD21" s="3" t="n">
-        <v>5322.4</v>
-      </c>
-      <c r="AE21" s="3" t="n">
-        <v>5269.18</v>
-      </c>
-      <c r="AF21" s="3" t="n">
-        <v>5375.62</v>
-      </c>
-      <c r="AG21" s="3" t="n">
-        <v>5056.28</v>
-      </c>
-      <c r="AH21" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI21" s="3" t="n">
-        <v>5748.192</v>
-      </c>
-      <c r="AJ21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>6120.759999999999</v>
-      </c>
-      <c r="AL21" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM21" s="3" t="n">
-        <v>5570</v>
-      </c>
-      <c r="AN21" s="3" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="AO21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" s="3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AQ21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19 03:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>R2-BAJAJHLDNG-IND-20260731-2751d1</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG_IND_20260731</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr"/>
-      <c r="U22" s="3" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="X22" s="3" t="inlineStr"/>
-      <c r="Y22" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA22" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB22" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AC22" s="3" t="n">
-        <v>11127</v>
-      </c>
-      <c r="AD22" s="3" t="n">
-        <v>11127</v>
-      </c>
-      <c r="AE22" s="3" t="n">
-        <v>11015.73</v>
-      </c>
-      <c r="AF22" s="3" t="n">
-        <v>11238.27</v>
-      </c>
-      <c r="AG22" s="3" t="n">
-        <v>10570.65</v>
-      </c>
-      <c r="AH22" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>12017.16</v>
-      </c>
-      <c r="AJ22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>12796.05</v>
-      </c>
-      <c r="AL22" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM22" s="3" t="n">
-        <v>11379</v>
-      </c>
-      <c r="AN22" s="3" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AO22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="3" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AQ22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19 03:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>R2-LICI-IND-20260805-a4f409</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>LICI_IND_20260805</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr"/>
-      <c r="U23" s="3" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="X23" s="3" t="inlineStr"/>
-      <c r="Y23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA23" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC23" s="3" t="n">
-        <v>391.3</v>
-      </c>
-      <c r="AD23" s="3" t="n">
-        <v>391.3</v>
-      </c>
-      <c r="AE23" s="3" t="n">
-        <v>387.39</v>
-      </c>
-      <c r="AF23" s="3" t="n">
-        <v>395.21</v>
-      </c>
-      <c r="AG23" s="3" t="n">
-        <v>371.735</v>
-      </c>
-      <c r="AH23" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI23" s="3" t="n">
-        <v>422.604</v>
-      </c>
-      <c r="AJ23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>449.995</v>
-      </c>
-      <c r="AL23" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM23" s="3" t="n">
-        <v>410</v>
-      </c>
-      <c r="AN23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19 03:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>TIINDIA_IND_20260805</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr"/>
-      <c r="U24" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="X24" s="3" t="inlineStr"/>
-      <c r="Y24" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA24" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC24" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AD24" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AE24" s="3" t="n">
-        <v>2716.86</v>
-      </c>
-      <c r="AF24" s="3" t="n">
-        <v>2771.74</v>
-      </c>
-      <c r="AG24" s="3" t="n">
-        <v>2607.085</v>
-      </c>
-      <c r="AH24" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI24" s="3" t="n">
-        <v>2963.844000000001</v>
-      </c>
-      <c r="AJ24" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK24" s="3" t="n">
-        <v>3155.945</v>
-      </c>
-      <c r="AL24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM24" s="3" t="n">
-        <v>2741.4</v>
-      </c>
-      <c r="AN24" s="3" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="AO24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" s="3" t="inlineStr"/>
-      <c r="AS24" s="3" t="inlineStr"/>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19 03:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>R1-KOTAKBANK-IND-20260801-373ce0</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK_IND_20260801</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Kotak Bank</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA25" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="AC25" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AD25" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AE25" s="3" t="n">
-        <v>385.41</v>
-      </c>
-      <c r="AF25" s="3" t="n">
-        <v>393.19</v>
-      </c>
-      <c r="AG25" s="3" t="n">
-        <v>369.835</v>
-      </c>
-      <c r="AH25" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI25" s="3" t="n">
-        <v>420.444</v>
-      </c>
-      <c r="AJ25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>447.695</v>
-      </c>
-      <c r="AL25" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM25" s="3" t="n">
-        <v>392.7</v>
-      </c>
-      <c r="AN25" s="3" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="AO25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" s="3" t="inlineStr"/>
-      <c r="AS25" s="3" t="inlineStr"/>
-      <c r="AT25" s="3" t="inlineStr"/>
-      <c r="AU25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19 03:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>R1-BRITANNIA-IND-20260801-025f04</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA_IND_20260801</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr"/>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA26" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="AC26" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AD26" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AE26" s="3" t="n">
-        <v>5351.94</v>
-      </c>
-      <c r="AF26" s="3" t="n">
-        <v>5460.06</v>
-      </c>
-      <c r="AG26" s="3" t="n">
-        <v>5135.7</v>
-      </c>
-      <c r="AH26" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI26" s="3" t="n">
-        <v>5838.48</v>
-      </c>
-      <c r="AJ26" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK26" s="3" t="n">
-        <v>6216.9</v>
-      </c>
-      <c r="AL26" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM26" s="3" t="n">
-        <v>5521</v>
-      </c>
-      <c r="AN26" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="AO26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="3" t="inlineStr"/>
-      <c r="AS26" s="3" t="inlineStr"/>
-      <c r="AT26" s="3" t="inlineStr"/>
-      <c r="AU26" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19 03:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>R1-TATAPOWER-IND-20260804-dafbb4</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER_IND_20260804</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr"/>
-      <c r="U27" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="X27" s="3" t="inlineStr"/>
-      <c r="Y27" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA27" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AD27" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AE27" s="3" t="n">
-        <v>377.78</v>
-      </c>
-      <c r="AF27" s="3" t="n">
-        <v>385.42</v>
-      </c>
-      <c r="AG27" s="3" t="n">
-        <v>362.52</v>
-      </c>
-      <c r="AH27" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI27" s="3" t="n">
-        <v>412.128</v>
-      </c>
-      <c r="AJ27" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK27" s="3" t="n">
-        <v>438.84</v>
-      </c>
-      <c r="AL27" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM27" s="3" t="n">
-        <v>381.5</v>
-      </c>
-      <c r="AN27" s="3" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AO27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="3" t="inlineStr"/>
-      <c r="AS27" s="3" t="inlineStr"/>
-      <c r="AT27" s="3" t="inlineStr"/>
-      <c r="AU27" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19 03:59</t>
+          <t>2026-08-19 14:52</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV27"/>
+  <autoFilter ref="A1:AV20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>